--- a/Registro bauchers.xlsx
+++ b/Registro bauchers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFE346E-D430-44A8-B1AC-EA44E28C5D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F2C7BF-69D4-4CB9-8D82-F1F914050F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="120">
   <si>
     <t xml:space="preserve">Concepto </t>
   </si>
@@ -687,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -729,24 +729,12 @@
     <xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -755,7 +743,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,13 +929,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -948,6 +938,13 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -991,7 +988,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{508F432E-70D2-4776-8C1A-19702FD4ACFD}" name="TablaDatos" displayName="TablaDatos" ref="A1:I83" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{508F432E-70D2-4776-8C1A-19702FD4ACFD}" name="TablaDatos" displayName="TablaDatos" ref="A1:I83" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F17">
     <sortCondition ref="D1:D17"/>
   </sortState>
@@ -1378,10 +1375,10 @@
       <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>116</v>
       </c>
       <c r="M1" t="s">
@@ -1417,7 +1414,9 @@
         <f t="shared" ref="I2:I38" si="0">TEXT(D2,"mmmm")</f>
         <v>enero</v>
       </c>
-      <c r="K2" s="37"/>
+      <c r="K2" s="33" t="s">
+        <v>62</v>
+      </c>
       <c r="M2" t="s">
         <v>41</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>78</v>
       </c>
       <c r="I19" s="11" t="str">
-        <f>TEXT(D19,"mmmm")</f>
+        <f t="shared" ref="I19:I35" si="1">TEXT(D19,"mmmm")</f>
         <v>enero</v>
       </c>
     </row>
@@ -1975,7 +1974,7 @@
         <v>78</v>
       </c>
       <c r="I20" s="11" t="str">
-        <f>TEXT(D20,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2005,7 +2004,7 @@
         <v>78</v>
       </c>
       <c r="I21" s="11" t="str">
-        <f>TEXT(D21,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2035,7 +2034,7 @@
         <v>78</v>
       </c>
       <c r="I22" s="11" t="str">
-        <f>TEXT(D22,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2065,7 +2064,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="11" t="str">
-        <f>TEXT(D23,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2095,7 +2094,7 @@
         <v>78</v>
       </c>
       <c r="I24" s="11" t="str">
-        <f>TEXT(D24,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2125,7 +2124,7 @@
         <v>78</v>
       </c>
       <c r="I25" s="11" t="str">
-        <f>TEXT(D25,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2155,7 +2154,7 @@
         <v>78</v>
       </c>
       <c r="I26" s="11" t="str">
-        <f>TEXT(D26,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2185,7 +2184,7 @@
         <v>78</v>
       </c>
       <c r="I27" s="11" t="str">
-        <f>TEXT(D27,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2215,7 +2214,7 @@
         <v>96</v>
       </c>
       <c r="I28" s="11" t="str">
-        <f>TEXT(D28,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2245,7 +2244,7 @@
         <v>96</v>
       </c>
       <c r="I29" s="11" t="str">
-        <f>TEXT(D29,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>enero</v>
       </c>
     </row>
@@ -2275,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="11" t="str">
-        <f>TEXT(D30,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2305,7 +2304,7 @@
         <v>78</v>
       </c>
       <c r="I31" s="11" t="str">
-        <f>TEXT(D31,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2335,7 +2334,7 @@
         <v>78</v>
       </c>
       <c r="I32" s="11" t="str">
-        <f>TEXT(D32,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2365,7 +2364,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="11" t="str">
-        <f>TEXT(D33,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2395,7 +2394,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="11" t="str">
-        <f>TEXT(D34,"mmmm")</f>
+        <f t="shared" si="1"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2424,8 +2423,8 @@
       <c r="H35" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I35" s="36" t="str">
-        <f>TEXT(D35,"mmmm")</f>
+      <c r="I35" s="11" t="str">
+        <f t="shared" si="1"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2544,7 +2543,7 @@
       <c r="H39" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="31" t="str">
+      <c r="I39" s="30" t="str">
         <f>TEXT(D39,"mmmm")</f>
         <v>febrero</v>
       </c>
@@ -2575,7 +2574,7 @@
         <v>96</v>
       </c>
       <c r="I40" s="11" t="str">
-        <f t="shared" ref="I40:I61" si="1">TEXT(D40,"mmmm")</f>
+        <f t="shared" ref="I40:I61" si="2">TEXT(D40,"mmmm")</f>
         <v>febrero</v>
       </c>
     </row>
@@ -2605,7 +2604,7 @@
         <v>87</v>
       </c>
       <c r="I41" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2635,7 +2634,7 @@
         <v>11</v>
       </c>
       <c r="I42" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2665,7 +2664,7 @@
         <v>78</v>
       </c>
       <c r="I43" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2695,7 +2694,7 @@
         <v>78</v>
       </c>
       <c r="I44" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2725,7 +2724,7 @@
         <v>78</v>
       </c>
       <c r="I45" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2755,7 +2754,7 @@
         <v>78</v>
       </c>
       <c r="I46" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2785,7 +2784,7 @@
         <v>78</v>
       </c>
       <c r="I47" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2815,7 +2814,7 @@
         <v>78</v>
       </c>
       <c r="I48" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2845,7 +2844,7 @@
         <v>87</v>
       </c>
       <c r="I49" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2875,7 +2874,7 @@
         <v>78</v>
       </c>
       <c r="I50" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2905,7 +2904,7 @@
         <v>78</v>
       </c>
       <c r="I51" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>febrero</v>
       </c>
     </row>
@@ -2919,7 +2918,7 @@
       <c r="G52" s="13"/>
       <c r="H52" s="1"/>
       <c r="I52" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -2933,7 +2932,7 @@
       <c r="G53" s="13"/>
       <c r="H53" s="1"/>
       <c r="I53" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -2947,7 +2946,7 @@
       <c r="G54" s="13"/>
       <c r="H54" s="1"/>
       <c r="I54" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -2961,7 +2960,7 @@
       <c r="G55" s="13"/>
       <c r="H55" s="1"/>
       <c r="I55" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -2975,7 +2974,7 @@
       <c r="G56" s="13"/>
       <c r="H56" s="1"/>
       <c r="I56" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -2989,7 +2988,7 @@
       <c r="G57" s="13"/>
       <c r="H57" s="1"/>
       <c r="I57" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -3003,7 +3002,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="1"/>
       <c r="I58" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -3017,7 +3016,7 @@
       <c r="G59" s="13"/>
       <c r="H59" s="1"/>
       <c r="I59" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -3031,7 +3030,7 @@
       <c r="G60" s="13"/>
       <c r="H60" s="1"/>
       <c r="I60" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
@@ -3045,315 +3044,315 @@
       <c r="G61" s="13"/>
       <c r="H61" s="1"/>
       <c r="I61" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>enero</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="38"/>
+      <c r="A62" s="34"/>
       <c r="B62" s="20"/>
-      <c r="C62" s="39"/>
+      <c r="C62" s="35"/>
       <c r="D62" s="11"/>
       <c r="E62" s="11"/>
       <c r="F62" s="11"/>
       <c r="G62" s="13"/>
       <c r="H62" s="1"/>
       <c r="I62" s="11" t="str">
-        <f t="shared" ref="I62:I69" si="2">TEXT(D62,"mmmm")</f>
+        <f t="shared" ref="I62:I69" si="3">TEXT(D62,"mmmm")</f>
         <v>enero</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="38"/>
+      <c r="A63" s="34"/>
       <c r="B63" s="20"/>
-      <c r="C63" s="39"/>
+      <c r="C63" s="35"/>
       <c r="D63" s="11"/>
       <c r="E63" s="11"/>
       <c r="F63" s="11"/>
       <c r="G63" s="13"/>
       <c r="H63" s="1"/>
       <c r="I63" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="38"/>
+      <c r="A64" s="34"/>
       <c r="B64" s="20"/>
-      <c r="C64" s="39"/>
+      <c r="C64" s="35"/>
       <c r="D64" s="11"/>
       <c r="E64" s="11"/>
       <c r="F64" s="11"/>
       <c r="G64" s="13"/>
       <c r="H64" s="1"/>
       <c r="I64" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="38"/>
+      <c r="A65" s="34"/>
       <c r="B65" s="20"/>
-      <c r="C65" s="39"/>
+      <c r="C65" s="35"/>
       <c r="D65" s="11"/>
       <c r="E65" s="11"/>
       <c r="F65" s="11"/>
       <c r="G65" s="13"/>
       <c r="H65" s="1"/>
       <c r="I65" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="38"/>
+      <c r="A66" s="34"/>
       <c r="B66" s="20"/>
-      <c r="C66" s="39"/>
+      <c r="C66" s="35"/>
       <c r="D66" s="11"/>
       <c r="E66" s="11"/>
       <c r="F66" s="11"/>
       <c r="G66" s="13"/>
       <c r="H66" s="1"/>
       <c r="I66" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="38"/>
+      <c r="A67" s="34"/>
       <c r="B67" s="20"/>
-      <c r="C67" s="39"/>
+      <c r="C67" s="35"/>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
       <c r="F67" s="11"/>
       <c r="G67" s="13"/>
       <c r="H67" s="1"/>
       <c r="I67" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="38"/>
+      <c r="A68" s="34"/>
       <c r="B68" s="20"/>
-      <c r="C68" s="39"/>
+      <c r="C68" s="35"/>
       <c r="D68" s="11"/>
       <c r="E68" s="11"/>
       <c r="F68" s="11"/>
       <c r="G68" s="13"/>
       <c r="H68" s="1"/>
       <c r="I68" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="40"/>
+      <c r="A69" s="36"/>
       <c r="B69" s="21"/>
-      <c r="C69" s="30"/>
+      <c r="C69" s="29"/>
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
       <c r="F69" s="14"/>
-      <c r="G69" s="41"/>
+      <c r="G69" s="37"/>
       <c r="H69" s="4"/>
       <c r="I69" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>enero</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="38"/>
+      <c r="A70" s="34"/>
       <c r="B70" s="20"/>
-      <c r="C70" s="39"/>
+      <c r="C70" s="35"/>
       <c r="D70" s="11"/>
       <c r="E70" s="11"/>
       <c r="F70" s="11"/>
       <c r="G70" s="13"/>
       <c r="H70" s="1"/>
       <c r="I70" s="11" t="str">
-        <f t="shared" ref="I70:I83" si="3">TEXT(D70,"mmmm")</f>
+        <f t="shared" ref="I70:I83" si="4">TEXT(D70,"mmmm")</f>
         <v>enero</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="38"/>
+      <c r="A71" s="34"/>
       <c r="B71" s="20"/>
-      <c r="C71" s="39"/>
+      <c r="C71" s="35"/>
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
       <c r="G71" s="13"/>
       <c r="H71" s="1"/>
       <c r="I71" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="38"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="20"/>
-      <c r="C72" s="39"/>
+      <c r="C72" s="35"/>
       <c r="D72" s="11"/>
       <c r="E72" s="11"/>
       <c r="F72" s="11"/>
       <c r="G72" s="13"/>
       <c r="H72" s="1"/>
       <c r="I72" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="38"/>
+      <c r="A73" s="34"/>
       <c r="B73" s="20"/>
-      <c r="C73" s="39"/>
+      <c r="C73" s="35"/>
       <c r="D73" s="11"/>
       <c r="E73" s="11"/>
       <c r="F73" s="11"/>
       <c r="G73" s="13"/>
       <c r="H73" s="1"/>
       <c r="I73" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="38"/>
+      <c r="A74" s="34"/>
       <c r="B74" s="20"/>
-      <c r="C74" s="39"/>
+      <c r="C74" s="35"/>
       <c r="D74" s="11"/>
       <c r="E74" s="11"/>
       <c r="F74" s="11"/>
       <c r="G74" s="13"/>
       <c r="H74" s="1"/>
       <c r="I74" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="38"/>
+      <c r="A75" s="34"/>
       <c r="B75" s="20"/>
-      <c r="C75" s="39"/>
+      <c r="C75" s="35"/>
       <c r="D75" s="11"/>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
       <c r="G75" s="13"/>
       <c r="H75" s="1"/>
       <c r="I75" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="38"/>
+      <c r="A76" s="34"/>
       <c r="B76" s="20"/>
-      <c r="C76" s="39"/>
+      <c r="C76" s="35"/>
       <c r="D76" s="11"/>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
       <c r="G76" s="13"/>
       <c r="H76" s="1"/>
       <c r="I76" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="38"/>
+      <c r="A77" s="34"/>
       <c r="B77" s="20"/>
-      <c r="C77" s="39"/>
+      <c r="C77" s="35"/>
       <c r="D77" s="11"/>
       <c r="E77" s="11"/>
       <c r="F77" s="11"/>
       <c r="G77" s="13"/>
       <c r="H77" s="1"/>
       <c r="I77" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="38"/>
+      <c r="A78" s="34"/>
       <c r="B78" s="20"/>
-      <c r="C78" s="39"/>
+      <c r="C78" s="35"/>
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="11"/>
       <c r="G78" s="13"/>
       <c r="H78" s="1"/>
       <c r="I78" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="38"/>
+      <c r="A79" s="34"/>
       <c r="B79" s="20"/>
-      <c r="C79" s="39"/>
+      <c r="C79" s="35"/>
       <c r="D79" s="11"/>
       <c r="E79" s="11"/>
       <c r="F79" s="11"/>
       <c r="G79" s="13"/>
       <c r="H79" s="1"/>
       <c r="I79" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="38"/>
+      <c r="A80" s="34"/>
       <c r="B80" s="20"/>
-      <c r="C80" s="39"/>
+      <c r="C80" s="35"/>
       <c r="D80" s="11"/>
       <c r="E80" s="11"/>
       <c r="F80" s="11"/>
       <c r="G80" s="13"/>
       <c r="H80" s="1"/>
       <c r="I80" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="38"/>
+      <c r="A81" s="34"/>
       <c r="B81" s="20"/>
-      <c r="C81" s="39"/>
+      <c r="C81" s="35"/>
       <c r="D81" s="11"/>
       <c r="E81" s="11"/>
       <c r="F81" s="11"/>
       <c r="G81" s="13"/>
       <c r="H81" s="1"/>
       <c r="I81" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="38"/>
+      <c r="A82" s="34"/>
       <c r="B82" s="20"/>
-      <c r="C82" s="39"/>
+      <c r="C82" s="35"/>
       <c r="D82" s="11"/>
       <c r="E82" s="11"/>
       <c r="F82" s="11"/>
       <c r="G82" s="13"/>
       <c r="H82" s="1"/>
       <c r="I82" s="11" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="40"/>
+      <c r="A83" s="36"/>
       <c r="B83" s="21"/>
-      <c r="C83" s="30"/>
+      <c r="C83" s="29"/>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
-      <c r="G83" s="41"/>
+      <c r="G83" s="37"/>
       <c r="H83" s="4"/>
       <c r="I83" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>enero</v>
       </c>
     </row>
@@ -3396,17 +3395,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C3" s="26" t="s">
@@ -3433,7 +3432,7 @@
       <c r="J3" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="K3" s="33" t="s">
+      <c r="K3" s="32" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3474,48 +3473,48 @@
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="J7" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="K7" s="32" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3559,48 +3558,48 @@
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="42" t="s">
+      <c r="J13" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="33" t="s">
+      <c r="K13" s="32" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3647,48 +3646,48 @@
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="29"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="G19" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="42" t="s">
+      <c r="J19" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="32" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3813,48 +3812,48 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E27" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="42" t="s">
+      <c r="G27" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H27" s="42" t="s">
+      <c r="H27" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I27" s="42" t="s">
+      <c r="I27" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="42" t="s">
+      <c r="J27" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="33" t="s">
+      <c r="K27" s="32" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3985,53 +3984,53 @@
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="42" t="s">
+      <c r="D35" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="42" t="s">
+      <c r="E35" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="F35" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="G35" s="42" t="s">
+      <c r="G35" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H35" s="42" t="s">
+      <c r="H35" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="I35" s="42" t="s">
+      <c r="I35" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="J35" s="42" t="s">
+      <c r="J35" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="K35" s="33" t="s">
+      <c r="K35" s="32" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="39" t="s">
         <v>102</v>
       </c>
       <c r="C36" t="str" cm="1">
@@ -4371,12 +4370,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B34:K34"/>
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B12:K12"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B26:K26"/>
-    <mergeCell ref="B34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Registro bauchers.xlsx
+++ b/Registro bauchers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\Planos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F2C7BF-69D4-4CB9-8D82-F1F914050F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6893A96B-4074-411D-A084-9A69273692D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0DC1D28-234D-4551-8CE5-CF61D1F09C93}"/>
   </bookViews>
@@ -744,13 +744,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2720,8 +2720,8 @@
       <c r="G45" s="13">
         <v>1510</v>
       </c>
-      <c r="H45" s="22" t="s">
-        <v>78</v>
+      <c r="H45" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="I45" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2870,8 +2870,8 @@
       <c r="G50" s="13">
         <v>1510</v>
       </c>
-      <c r="H50" s="22" t="s">
-        <v>78</v>
+      <c r="H50" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="I50" s="11" t="str">
         <f t="shared" si="2"/>
@@ -2900,8 +2900,8 @@
       <c r="G51" s="13">
         <v>1510</v>
       </c>
-      <c r="H51" s="22" t="s">
-        <v>78</v>
+      <c r="H51" s="27" t="s">
+        <v>96</v>
       </c>
       <c r="I51" s="11" t="str">
         <f t="shared" si="2"/>
@@ -3395,17 +3395,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C3" s="26" t="s">
@@ -3473,18 +3473,18 @@
       <c r="I5" s="9"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
@@ -3545,7 +3545,7 @@
         <v>1510</v>
       </c>
       <c r="J8" t="str">
-        <v>Espera</v>
+        <v>Aprovados</v>
       </c>
       <c r="K8" t="str">
         <v>febrero</v>
@@ -3558,18 +3558,18 @@
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
@@ -3646,18 +3646,18 @@
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="40"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="38" t="s">
@@ -3812,18 +3812,18 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+      <c r="I26" s="40"/>
+      <c r="J26" s="40"/>
+      <c r="K26" s="40"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="38" t="s">
@@ -3984,18 +3984,18 @@
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="26" t="s">
@@ -4034,7 +4034,7 @@
         <v>102</v>
       </c>
       <c r="C36" t="str" cm="1">
-        <f t="array" ref="C36:K38">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!H2:H1000= B36, "No hay registros")</f>
+        <f t="array" ref="C36:K41">_xlfn._xlws.FILTER('BAUCHER 2026'!A2:I1000, 'BAUCHER 2026'!H2:H1000= B36, "No hay registros")</f>
         <v>T-4CHCQK</v>
       </c>
       <c r="D36" t="str">
@@ -4121,22 +4121,91 @@
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="9"/>
+      <c r="C39" t="str">
+        <v>T-4CI3L3</v>
+      </c>
+      <c r="D39" t="str">
+        <v>CARMEN CECILIA FLORES GUTIERREZ</v>
+      </c>
+      <c r="E39" t="str">
+        <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
+      </c>
+      <c r="F39" s="7">
+        <v>46066</v>
+      </c>
+      <c r="G39" s="7">
+        <v>46087</v>
+      </c>
+      <c r="H39" s="7">
+        <v>46066</v>
+      </c>
+      <c r="I39" s="9">
+        <v>1510</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Aprovados</v>
+      </c>
+      <c r="K39" t="str">
+        <v>febrero</v>
+      </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="9"/>
+      <c r="C40" t="str">
+        <v>T-4CILAP</v>
+      </c>
+      <c r="D40" t="str">
+        <v>GREGORY HERNANDEZ</v>
+      </c>
+      <c r="E40" t="str">
+        <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
+      </c>
+      <c r="F40" s="7">
+        <v>46078</v>
+      </c>
+      <c r="G40" s="7">
+        <v>46099</v>
+      </c>
+      <c r="H40" s="7">
+        <v>46078</v>
+      </c>
+      <c r="I40" s="9">
+        <v>1510</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Aprovados</v>
+      </c>
+      <c r="K40" t="str">
+        <v>febrero</v>
+      </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="9"/>
+      <c r="C41" t="str">
+        <v>T-4CILBE</v>
+      </c>
+      <c r="D41" t="str">
+        <v>GREGORY HERNANDEZ</v>
+      </c>
+      <c r="E41" t="str">
+        <v>APROVACION Y REVICIÓN DE PLANOS TOPOGRAFICOS CON FINES CATASTRALES</v>
+      </c>
+      <c r="F41" s="7">
+        <v>46078</v>
+      </c>
+      <c r="G41" s="7">
+        <v>46099</v>
+      </c>
+      <c r="H41" s="7">
+        <v>46078</v>
+      </c>
+      <c r="I41" s="9">
+        <v>1510</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Aprovados</v>
+      </c>
+      <c r="K41" t="str">
+        <v>febrero</v>
+      </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F43" s="7"/>
